--- a/Data/FlightPlan/FPL_28SEP26.xlsx
+++ b/Data/FlightPlan/FPL_28SEP26.xlsx
@@ -473,6 +473,9 @@
     <t>18:00</t>
   </si>
   <si>
+    <t>19:59</t>
+  </si>
+  <si>
     <t>01:20</t>
   </si>
   <si>
@@ -761,6 +764,9 @@
     <t>16:45</t>
   </si>
   <si>
+    <t>22:21</t>
+  </si>
+  <si>
     <t>VN-A551</t>
   </si>
   <si>
@@ -1178,7 +1184,7 @@
     <t>12:58</t>
   </si>
   <si>
-    <t>18:29</t>
+    <t>19:03</t>
   </si>
   <si>
     <t>21:40</t>
@@ -1298,9 +1304,6 @@
     <t>14:57</t>
   </si>
   <si>
-    <t>17:57</t>
-  </si>
-  <si>
     <t>VN-A658</t>
   </si>
   <si>
@@ -1601,6 +1604,9 @@
     <t>OVB</t>
   </si>
   <si>
+    <t>04:20</t>
+  </si>
+  <si>
     <t>VN-A815</t>
   </si>
   <si>
@@ -1643,7 +1649,7 @@
     <t>Total Record(s): 373</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 28, 2026 16:50</t>
+    <t xml:space="preserve">Generated on  Sep 28, 2026 17:02</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4126,7 +4132,9 @@
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
+      <c t="s" r="M68" s="7">
+        <v>154</v>
+      </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c t="s" r="A69" s="6">
@@ -4152,10 +4160,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -4188,7 +4196,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4200,15 +4208,15 @@
         <v>89</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -4223,7 +4231,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -4238,12 +4246,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -4258,7 +4266,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4278,7 +4286,7 @@
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4293,7 +4301,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4305,7 +4313,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J74" s="7">
         <v>52</v>
@@ -4315,7 +4323,7 @@
       </c>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4330,7 +4338,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4342,7 +4350,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>138</v>
@@ -4367,7 +4375,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4382,7 +4390,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="K76" s="7">
         <v>90</v>
@@ -4419,7 +4427,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4428,18 +4436,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4454,27 +4462,27 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4489,7 +4497,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4509,7 +4517,7 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4524,7 +4532,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4536,17 +4544,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="K81" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4561,7 +4569,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4579,11 +4587,11 @@
         <v>107</v>
       </c>
       <c t="s" r="K82" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4598,7 +4606,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4610,17 +4618,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="K83" s="7">
         <v>43</v>
       </c>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4650,19 +4658,19 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>132</v>
@@ -4670,7 +4678,7 @@
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4685,7 +4693,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4705,7 +4713,7 @@
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4720,7 +4728,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4732,10 +4740,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4753,7 +4761,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4762,13 +4770,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4786,22 +4794,22 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4834,7 +4842,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4846,15 +4854,15 @@
         <v>24</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4869,7 +4877,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4884,12 +4892,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -4904,7 +4912,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4913,18 +4921,18 @@
         <v>89</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -4939,27 +4947,27 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -4974,7 +4982,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4986,10 +4994,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -5007,7 +5015,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -5019,10 +5027,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -5055,7 +5063,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5064,10 +5072,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>18</v>
@@ -5075,7 +5083,7 @@
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -5090,13 +5098,13 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>16</v>
@@ -5105,12 +5113,12 @@
         <v>122</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -5125,7 +5133,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5160,7 +5168,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5175,12 +5183,12 @@
         <v>35</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -5195,7 +5203,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5204,10 +5212,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>105</v>
@@ -5215,7 +5223,7 @@
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5230,13 +5238,13 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>16</v>
@@ -5245,7 +5253,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -5263,7 +5271,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5275,7 +5283,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>31</v>
@@ -5311,7 +5319,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5346,7 +5354,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5358,15 +5366,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5381,7 +5389,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5390,10 +5398,10 @@
         <v>82</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>122</v>
@@ -5429,7 +5437,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5441,7 +5449,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>112</v>
@@ -5449,7 +5457,7 @@
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5464,7 +5472,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5479,12 +5487,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5499,7 +5507,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5508,7 +5516,7 @@
         <v>82</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="I112" s="7">
         <v>149</v>
@@ -5519,7 +5527,7 @@
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5534,19 +5542,19 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>65</v>
@@ -5569,7 +5577,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5584,12 +5592,12 @@
         <v>73</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5604,7 +5612,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5616,7 +5624,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>30</v>
@@ -5639,7 +5647,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5651,10 +5659,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5672,7 +5680,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5684,10 +5692,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5705,7 +5713,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5714,13 +5722,13 @@
         <v>82</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5753,7 +5761,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5765,15 +5773,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5788,7 +5796,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5800,15 +5808,15 @@
         <v>142</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5823,7 +5831,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5835,14 +5843,16 @@
         <v>82</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
-      <c r="M122" s="7"/>
+      <c t="s" r="M122" s="7">
+        <v>251</v>
+      </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c r="A123" s="6"/>
@@ -5871,7 +5881,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5883,7 +5893,7 @@
         <v>121</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>100</v>
@@ -5891,7 +5901,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5906,7 +5916,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5921,7 +5931,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5941,7 +5951,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5953,17 +5963,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="K126" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5978,7 +5988,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5990,7 +6000,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>113</v>
@@ -6026,7 +6036,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6041,10 +6051,10 @@
         <v>84</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="K129" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
@@ -6063,7 +6073,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6085,7 +6095,7 @@
       </c>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6100,7 +6110,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6109,13 +6119,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -6133,22 +6143,22 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -6181,19 +6191,19 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>45</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>98</v>
@@ -6201,7 +6211,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6216,7 +6226,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6225,10 +6235,10 @@
         <v>45</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>62</v>
@@ -6260,26 +6270,26 @@
         <v>7615</v>
       </c>
       <c t="s" r="C137" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -6295,11 +6305,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C138" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6311,7 +6321,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>48</v>
@@ -6319,7 +6329,7 @@
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6334,7 +6344,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6349,7 +6359,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6382,7 +6392,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6397,12 +6407,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6417,7 +6427,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6432,12 +6442,12 @@
         <v>99</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6452,7 +6462,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6464,10 +6474,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6485,7 +6495,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6497,7 +6507,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>43</v>
@@ -6518,7 +6528,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6527,13 +6537,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6566,7 +6576,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6578,15 +6588,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6601,7 +6611,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6610,13 +6620,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6634,22 +6644,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6682,13 +6692,13 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>16</v>
@@ -6702,7 +6712,7 @@
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6717,7 +6727,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6732,7 +6742,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6750,7 +6760,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6762,10 +6772,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6783,7 +6793,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6798,7 +6808,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6831,7 +6841,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6843,7 +6853,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>111</v>
@@ -6851,7 +6861,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -6866,7 +6876,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6875,10 +6885,10 @@
         <v>45</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>151</v>
@@ -6901,13 +6911,13 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>45</v>
@@ -6916,7 +6926,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6949,7 +6959,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6961,7 +6971,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>60</v>
@@ -6969,7 +6979,7 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -6984,7 +6994,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6996,7 +7006,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>129</v>
@@ -7004,7 +7014,7 @@
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -7019,7 +7029,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7028,18 +7038,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -7054,27 +7064,27 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7089,7 +7099,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7098,13 +7108,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="I164" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -7122,13 +7132,13 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>16</v>
@@ -7137,7 +7147,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -7155,7 +7165,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7164,10 +7174,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>43</v>
@@ -7188,19 +7198,19 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>68</v>
@@ -7236,7 +7246,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7248,10 +7258,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -7271,7 +7281,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7280,18 +7290,18 @@
         <v>82</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7306,27 +7316,27 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7341,7 +7351,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7353,15 +7363,15 @@
         <v>51</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7376,7 +7386,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7424,7 +7434,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7444,7 +7454,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7459,7 +7469,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7471,15 +7481,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7494,7 +7504,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7509,12 +7519,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7529,7 +7539,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7538,10 +7548,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>55</v>
@@ -7549,7 +7559,7 @@
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7564,22 +7574,22 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7597,7 +7607,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7609,10 +7619,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7645,7 +7655,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7660,12 +7670,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7680,7 +7690,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7695,12 +7705,12 @@
         <v>149</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7715,7 +7725,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7735,7 +7745,7 @@
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7750,7 +7760,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7762,7 +7772,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>144</v>
@@ -7770,7 +7780,7 @@
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7785,7 +7795,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7797,7 +7807,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>77</v>
@@ -7805,7 +7815,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7820,7 +7830,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7835,7 +7845,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7853,7 +7863,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7862,10 +7872,10 @@
         <v>82</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>31</v>
@@ -7886,22 +7896,22 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7934,7 +7944,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7946,7 +7956,7 @@
         <v>131</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>129</v>
@@ -7954,7 +7964,7 @@
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -7969,7 +7979,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7981,7 +7991,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>74</v>
@@ -7989,7 +7999,7 @@
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8000,11 +8010,11 @@
         <v>8516</v>
       </c>
       <c t="s" r="C193" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8013,10 +8023,10 @@
         <v>89</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>42</v>
@@ -8024,7 +8034,7 @@
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8035,23 +8045,23 @@
         <v>8517</v>
       </c>
       <c t="s" r="C194" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>108</v>
@@ -8087,7 +8097,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8099,10 +8109,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -8122,7 +8132,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8134,17 +8144,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="K197" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8159,7 +8169,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8171,7 +8181,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>27</v>
@@ -8179,7 +8189,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8209,7 +8219,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8218,18 +8228,18 @@
         <v>82</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="I200" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8244,13 +8254,13 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>82</v>
@@ -8259,12 +8269,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8279,7 +8289,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8294,12 +8304,12 @@
         <v>74</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8314,7 +8324,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8329,14 +8339,14 @@
         <v>119</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="K203" s="7">
         <v>101</v>
       </c>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8351,7 +8361,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8366,10 +8376,10 @@
         <v>30</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="K204" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
@@ -8388,7 +8398,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8400,17 +8410,17 @@
         <v>82</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="K205" s="7">
         <v>106</v>
       </c>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8440,7 +8450,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8449,18 +8459,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8475,13 +8485,13 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>16</v>
@@ -8490,12 +8500,12 @@
         <v>149</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8510,7 +8520,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8519,10 +8529,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>28</v>
@@ -8530,7 +8540,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8545,22 +8555,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8578,7 +8588,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8587,20 +8597,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="K211" s="7">
         <v>42</v>
       </c>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8615,19 +8625,19 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>108</v>
@@ -8637,7 +8647,7 @@
       </c>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8667,7 +8677,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8679,7 +8689,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>84</v>
@@ -8702,7 +8712,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8711,7 +8721,7 @@
         <v>82</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>132</v>
@@ -8722,7 +8732,7 @@
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8737,19 +8747,19 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>28</v>
@@ -8757,7 +8767,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8772,7 +8782,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8784,10 +8794,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8820,7 +8830,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8832,7 +8842,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>19</v>
@@ -8855,7 +8865,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8867,7 +8877,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>23</v>
@@ -8875,7 +8885,7 @@
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8890,7 +8900,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8902,7 +8912,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>28</v>
@@ -8910,7 +8920,7 @@
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8925,7 +8935,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8937,15 +8947,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8960,7 +8970,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8972,13 +8982,13 @@
         <v>89</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="K223" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
@@ -8997,7 +9007,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9012,14 +9022,14 @@
         <v>90</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c t="s" r="K224" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9049,7 +9059,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9058,18 +9068,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9084,27 +9094,27 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9119,7 +9129,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9134,12 +9144,12 @@
         <v>149</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9154,7 +9164,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9166,15 +9176,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9189,7 +9199,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9198,18 +9208,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I230" s="7">
         <v>116</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9224,13 +9234,13 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>16</v>
@@ -9239,7 +9249,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -9257,7 +9267,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9269,17 +9279,17 @@
         <v>82</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="K232" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9294,7 +9304,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9306,13 +9316,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>139</v>
       </c>
       <c t="s" r="K233" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
@@ -9346,7 +9356,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9358,7 +9368,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>98</v>
@@ -9381,7 +9391,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9390,7 +9400,7 @@
         <v>82</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="I236" s="7">
         <v>25</v>
@@ -9401,7 +9411,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9416,22 +9426,22 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9449,7 +9459,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9461,10 +9471,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -9497,7 +9507,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9512,12 +9522,12 @@
         <v>112</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9532,7 +9542,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9544,15 +9554,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9567,7 +9577,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9576,13 +9586,13 @@
         <v>82</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>86</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9602,13 +9612,13 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>82</v>
@@ -9635,7 +9645,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9644,13 +9654,13 @@
         <v>82</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9683,7 +9693,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9695,15 +9705,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9718,7 +9728,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9730,7 +9740,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>28</v>
@@ -9738,7 +9748,7 @@
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9753,7 +9763,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9765,10 +9775,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9786,7 +9796,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9795,13 +9805,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9819,19 +9829,19 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>80</v>
@@ -9867,7 +9877,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9887,7 +9897,7 @@
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -9902,7 +9912,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9914,15 +9924,15 @@
         <v>89</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9937,7 +9947,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9952,7 +9962,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9972,7 +9982,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9984,7 +9994,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>138</v>
@@ -9992,7 +10002,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10007,7 +10017,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10019,10 +10029,10 @@
         <v>89</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -10055,7 +10065,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
@@ -10064,18 +10074,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10090,19 +10100,19 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>113</v>
@@ -10110,7 +10120,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10125,7 +10135,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F260" s="7">
         <v>320</v>
@@ -10137,7 +10147,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>84</v>
@@ -10145,7 +10155,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10160,7 +10170,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F261" s="7">
         <v>320</v>
@@ -10172,15 +10182,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10195,7 +10205,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
@@ -10204,10 +10214,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>133</v>
@@ -10215,7 +10225,7 @@
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10230,13 +10240,13 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>16</v>
@@ -10250,7 +10260,7 @@
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10265,7 +10275,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -10274,10 +10284,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>30</v>
@@ -10298,19 +10308,19 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>138</v>
@@ -10346,7 +10356,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10358,7 +10368,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>112</v>
@@ -10366,7 +10376,7 @@
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10381,7 +10391,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10396,12 +10406,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10416,7 +10426,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10425,7 +10435,7 @@
         <v>89</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="I269" s="7">
         <v>47</v>
@@ -10436,7 +10446,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10451,27 +10461,27 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10486,7 +10496,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10498,7 +10508,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>86</v>
@@ -10521,7 +10531,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10536,12 +10546,12 @@
         <v>135</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10571,7 +10581,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10580,18 +10590,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10606,13 +10616,13 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>16</v>
@@ -10621,12 +10631,12 @@
         <v>23</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10641,7 +10651,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10650,18 +10660,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c t="s" r="I276" s="7">
         <v>135</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10676,22 +10686,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10724,7 +10734,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10736,15 +10746,15 @@
         <v>89</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10759,7 +10769,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10771,15 +10781,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10794,7 +10804,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10809,12 +10819,12 @@
         <v>118</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10829,7 +10839,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10841,7 +10851,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>105</v>
@@ -10862,7 +10872,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10874,10 +10884,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10895,7 +10905,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10907,10 +10917,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10928,7 +10938,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10937,10 +10947,10 @@
         <v>82</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>19</v>
@@ -10976,7 +10986,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10985,10 +10995,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>62</v>
@@ -10996,7 +11006,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11011,27 +11021,27 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11046,7 +11056,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -11055,10 +11065,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>27</v>
@@ -11066,7 +11076,7 @@
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11081,13 +11091,13 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>16</v>
@@ -11096,12 +11106,12 @@
         <v>101</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>429</v>
+        <v>105</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11116,7 +11126,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11125,20 +11135,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="K291" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11153,13 +11163,13 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>16</v>
@@ -11168,10 +11178,10 @@
         <v>90</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="K292" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
@@ -11205,7 +11215,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -11214,10 +11224,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>46</v>
@@ -11225,7 +11235,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11240,27 +11250,27 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11275,7 +11285,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11284,10 +11294,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>129</v>
@@ -11295,7 +11305,7 @@
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11310,27 +11320,27 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11345,7 +11355,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11357,15 +11367,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11380,7 +11390,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -11400,7 +11410,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11415,7 +11425,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11433,7 +11443,7 @@
         <v>66</v>
       </c>
       <c t="s" r="K300" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
@@ -11452,7 +11462,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -11464,13 +11474,13 @@
         <v>29</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c t="s" r="K301" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
@@ -11504,7 +11514,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11516,15 +11526,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11539,7 +11549,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11551,7 +11561,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>37</v>
@@ -11559,7 +11569,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11574,7 +11584,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11586,15 +11596,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11609,7 +11619,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11621,10 +11631,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11642,7 +11652,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11651,13 +11661,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11675,22 +11685,22 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11723,7 +11733,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11738,7 +11748,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11758,7 +11768,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11778,7 +11788,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11793,7 +11803,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11805,7 +11815,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>55</v>
@@ -11828,7 +11838,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11840,10 +11850,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11861,7 +11871,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11873,10 +11883,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11909,7 +11919,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11921,10 +11931,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11944,7 +11954,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11962,11 +11972,11 @@
         <v>113</v>
       </c>
       <c t="s" r="K317" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11981,7 +11991,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11996,14 +12006,14 @@
         <v>47</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c t="s" r="K318" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12018,7 +12028,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -12027,18 +12037,18 @@
         <v>82</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c t="s" r="I319" s="7">
         <v>144</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12053,13 +12063,13 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>82</v>
@@ -12068,7 +12078,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -12101,7 +12111,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -12113,10 +12123,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -12136,7 +12146,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12151,10 +12161,10 @@
         <v>95</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="K323" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
@@ -12173,7 +12183,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12182,20 +12192,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="I324" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="K324" s="7">
         <v>22</v>
       </c>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12210,29 +12220,29 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>26</v>
       </c>
       <c t="s" r="K325" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12247,7 +12257,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12256,7 +12266,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c t="s" r="I326" s="7">
         <v>87</v>
@@ -12280,19 +12290,19 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>59</v>
@@ -12328,7 +12338,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12343,12 +12353,12 @@
         <v>59</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12363,7 +12373,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12378,12 +12388,12 @@
         <v>126</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12398,7 +12408,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12410,7 +12420,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>37</v>
@@ -12418,7 +12428,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12433,7 +12443,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12445,7 +12455,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>38</v>
@@ -12453,7 +12463,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12468,7 +12478,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12477,13 +12487,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -12501,13 +12511,13 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>16</v>
@@ -12549,7 +12559,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12564,12 +12574,12 @@
         <v>133</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12584,7 +12594,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12599,12 +12609,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12619,7 +12629,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12634,7 +12644,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -12652,7 +12662,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12664,7 +12674,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>80</v>
@@ -12700,7 +12710,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12709,18 +12719,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12735,19 +12745,19 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>73</v>
@@ -12755,7 +12765,7 @@
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12770,7 +12780,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12805,7 +12815,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12817,10 +12827,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12840,7 +12850,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12849,13 +12859,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>55</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12873,22 +12883,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12921,7 +12931,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12936,12 +12946,12 @@
         <v>112</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12956,7 +12966,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12976,7 +12986,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12991,7 +13001,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -13003,15 +13013,15 @@
         <v>24</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13026,7 +13036,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -13041,12 +13051,12 @@
         <v>144</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13061,7 +13071,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -13070,13 +13080,13 @@
         <v>82</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -13094,19 +13104,19 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>80</v>
@@ -13127,7 +13137,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13139,10 +13149,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -13175,13 +13185,13 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>16</v>
@@ -13190,10 +13200,10 @@
         <v>126</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="K356" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
@@ -13212,7 +13222,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13221,7 +13231,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>37</v>
@@ -13232,7 +13242,7 @@
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13247,22 +13257,22 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13280,7 +13290,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13289,13 +13299,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="I359" s="7">
         <v>147</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -13328,7 +13338,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -13340,15 +13350,15 @@
         <v>24</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13363,7 +13373,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -13375,15 +13385,15 @@
         <v>82</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13398,7 +13408,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -13407,13 +13417,13 @@
         <v>82</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -13433,13 +13443,13 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>82</v>
@@ -13448,12 +13458,12 @@
         <v>151</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13468,7 +13478,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13477,13 +13487,13 @@
         <v>82</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13501,22 +13511,22 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -13549,7 +13559,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13558,18 +13568,18 @@
         <v>82</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13584,13 +13594,13 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>82</v>
@@ -13604,7 +13614,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13619,7 +13629,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13628,10 +13638,10 @@
         <v>82</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>35</v>
@@ -13639,7 +13649,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13654,13 +13664,13 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>82</v>
@@ -13674,7 +13684,7 @@
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13689,7 +13699,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13698,18 +13708,18 @@
         <v>82</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>86</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13724,13 +13734,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>82</v>
@@ -13739,7 +13749,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="K373" s="7">
         <v>55</v>
@@ -13761,7 +13771,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13770,13 +13780,13 @@
         <v>82</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13794,22 +13804,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13842,7 +13852,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13851,18 +13861,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="I377" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13877,19 +13887,19 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>95</v>
@@ -13897,7 +13907,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13912,27 +13922,27 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -13947,13 +13957,13 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>16</v>
@@ -13982,7 +13992,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13994,7 +14004,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>86</v>
@@ -14002,7 +14012,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14017,7 +14027,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -14029,7 +14039,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>55</v>
@@ -14065,7 +14075,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14074,18 +14084,18 @@
         <v>82</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>140</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14100,19 +14110,19 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>21</v>
@@ -14120,7 +14130,7 @@
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14135,7 +14145,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14147,7 +14157,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>37</v>
@@ -14155,7 +14165,7 @@
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14170,7 +14180,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14179,18 +14189,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>133</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14205,13 +14215,13 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>16</v>
@@ -14220,7 +14230,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -14238,7 +14248,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14250,7 +14260,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>79</v>
@@ -14271,7 +14281,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -14283,10 +14293,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -14319,7 +14329,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -14354,7 +14364,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14363,18 +14373,18 @@
         <v>89</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14389,13 +14399,13 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>89</v>
@@ -14404,12 +14414,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14424,7 +14434,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14433,13 +14443,13 @@
         <v>89</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -14457,22 +14467,22 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -14505,13 +14515,13 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>82</v>
@@ -14520,7 +14530,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14540,7 +14550,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14552,7 +14562,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>37</v>
@@ -14575,7 +14585,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14610,7 +14620,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14622,15 +14632,15 @@
         <v>45</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14645,7 +14655,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14693,7 +14703,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14702,10 +14712,10 @@
         <v>82</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>95</v>
@@ -14713,7 +14723,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14728,19 +14738,19 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>63</v>
@@ -14748,7 +14758,7 @@
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14763,7 +14773,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14775,7 +14785,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>98</v>
@@ -14783,7 +14793,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14798,7 +14808,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14818,7 +14828,7 @@
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14833,7 +14843,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14842,13 +14852,13 @@
         <v>82</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14866,13 +14876,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>82</v>
@@ -14881,7 +14891,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14914,7 +14924,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14926,15 +14936,15 @@
         <v>142</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14949,7 +14959,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14961,15 +14971,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14984,7 +14994,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -15032,27 +15042,27 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15067,7 +15077,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -15102,7 +15112,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -15114,10 +15124,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -15135,7 +15145,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -15144,13 +15154,13 @@
         <v>82</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -15168,22 +15178,22 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -15216,7 +15226,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -15225,18 +15235,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15251,19 +15261,19 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>19</v>
@@ -15286,7 +15296,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -15298,15 +15308,15 @@
         <v>89</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15321,7 +15331,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -15336,7 +15346,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -15356,7 +15366,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -15378,7 +15388,7 @@
       </c>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15393,7 +15403,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15411,11 +15421,11 @@
         <v>153</v>
       </c>
       <c t="s" r="K426" s="7">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15445,7 +15455,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -15454,7 +15464,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="I428" s="7">
         <v>60</v>
@@ -15465,7 +15475,7 @@
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15480,19 +15490,19 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G429" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="H429" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>132</v>
@@ -15500,7 +15510,7 @@
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15515,7 +15525,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F430" s="7">
         <v>320</v>
@@ -15530,12 +15540,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15550,7 +15560,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -15559,10 +15569,10 @@
         <v>82</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>38</v>
@@ -15570,7 +15580,7 @@
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -15585,22 +15595,22 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -15629,11 +15639,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C434" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
@@ -15642,18 +15652,18 @@
         <v>45</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -15664,17 +15674,17 @@
         <v>5806</v>
       </c>
       <c t="s" r="C435" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>45</v>
@@ -15683,7 +15693,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -15716,13 +15726,13 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c t="s" r="H437" s="8">
         <v>16</v>
@@ -15736,7 +15746,7 @@
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -15751,7 +15761,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
@@ -15763,14 +15773,18 @@
         <v>45</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>87</v>
       </c>
-      <c r="K438" s="7"/>
+      <c t="s" r="K438" s="7">
+        <v>87</v>
+      </c>
       <c r="L438" s="7"/>
-      <c r="M438" s="7"/>
+      <c t="s" r="M438" s="7">
+        <v>350</v>
+      </c>
     </row>
     <row r="439" ht="14.25" customHeight="1">
       <c t="s" r="A439" s="6">
@@ -15784,7 +15798,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F439" s="7">
         <v>330</v>
@@ -15793,17 +15807,21 @@
         <v>45</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>444</v>
-      </c>
-      <c r="K439" s="7"/>
+        <v>445</v>
+      </c>
+      <c t="s" r="K439" s="7">
+        <v>424</v>
+      </c>
       <c r="L439" s="7"/>
-      <c r="M439" s="7"/>
+      <c t="s" r="M439" s="7">
+        <v>531</v>
+      </c>
     </row>
     <row r="440" ht="15" customHeight="1">
       <c r="A440" s="6"/>
@@ -15832,7 +15850,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
@@ -15841,7 +15859,7 @@
         <v>45</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c t="s" r="I441" s="7">
         <v>122</v>
@@ -15867,13 +15885,13 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F442" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>45</v>
@@ -15882,7 +15900,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -15915,7 +15933,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
@@ -15924,7 +15942,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c t="s" r="I444" s="7">
         <v>132</v>
@@ -15935,7 +15953,7 @@
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -15950,13 +15968,13 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F445" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>16</v>
@@ -15965,7 +15983,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15998,7 +16016,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
@@ -16010,15 +16028,15 @@
         <v>45</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -16033,7 +16051,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
@@ -16045,15 +16063,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -16068,7 +16086,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F449" s="7">
         <v>330</v>
@@ -16083,12 +16101,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -16118,7 +16136,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
@@ -16127,7 +16145,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c t="s" r="I451" s="7">
         <v>129</v>
@@ -16138,7 +16156,7 @@
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
       <c t="s" r="M451" s="7">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
@@ -16153,19 +16171,19 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c t="s" r="H452" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>59</v>
@@ -16176,7 +16194,7 @@
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c t="s" r="A453" s="9">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B453" s="9"/>
       <c r="C453" s="9"/>
@@ -16196,7 +16214,7 @@
     <row r="454" ht="65.25" customHeight="1"/>
     <row r="455" ht="17.25" customHeight="1">
       <c t="s" r="A455" s="10">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B455" s="10"/>
       <c r="C455" s="10"/>
@@ -16209,7 +16227,7 @@
       <c r="J455" s="10"/>
       <c r="K455" s="10"/>
       <c t="s" r="L455" s="11">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M455" s="11"/>
       <c r="N455" s="11"/>
